--- a/Pricing Logic/modules/uploads/module_4_1124.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1124.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,22 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>كوفى ميكس بونجورنو ظرف - 12 جم</t>
-  </si>
-  <si>
-    <t>سبرايت - 2.45 لتر</t>
-  </si>
-  <si>
-    <t>كوكا كولا - 2.45 لتر</t>
-  </si>
-  <si>
-    <t>رويال أعشاب كركديه - 20 فتلة</t>
-  </si>
-  <si>
-    <t>كوكاكولا اكشن - 300 مل</t>
-  </si>
-  <si>
-    <t>زيووو كرانشى الجبنة - 5 جنية</t>
+    <t>سبرايت - 1.45 لتر</t>
   </si>
   <si>
     <t>YES</t>
@@ -413,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -441,138 +426,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>59</v>
+        <v>2497</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>1740</v>
+        <v>185</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>59</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>72.5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>2775</v>
-      </c>
-      <c r="B4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>220.5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>2778</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>222.5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>4175</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1296</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>4175</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>6935</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>109.5</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>12345</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>47.5</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1124.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1124.xlsx
@@ -37,7 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>سبرايت - 1.45 لتر</t>
+    <t>بونكس - 9 كجم</t>
   </si>
   <si>
     <t>YES</t>
@@ -426,16 +426,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>2497</v>
+        <v>22327</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>185</v>
+        <v>688.5</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>

--- a/Pricing Logic/modules/uploads/module_4_1124.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1124.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,10 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>بونكس - 9 كجم</t>
+    <t>فانتا برتقال - 0.95 لتر</t>
+  </si>
+  <si>
+    <t>شويبس رمان بلاستيك - 250 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,19 +429,36 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22327</v>
+        <v>3673</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>688.5</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>11685</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>110</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1124.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1124.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,25 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>فانتا برتقال - 0.95 لتر</t>
-  </si>
-  <si>
-    <t>شويبس رمان بلاستيك - 250 مل</t>
+    <t>سمن كريستال ابيض - 1.5 كجم</t>
+  </si>
+  <si>
+    <t>بيبسى كانز جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>كوكا كولا جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>فانتا برتقال جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>ماكسى كانز ليمون نعناع اورجينال - 300 مل</t>
+  </si>
+  <si>
+    <t>ماكسي بـرتقال - 2 لتر</t>
+  </si>
+  <si>
+    <t>بيبسي هضبه - 250 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,24 +444,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>3673</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>122</v>
+        <v>600</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>11685</v>
+        <v>434</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -455,10 +470,95 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>110</v>
+        <v>298.5</v>
       </c>
       <c r="E3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>615</v>
+      </c>
+      <c r="B4" t="s">
         <v>9</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>305.5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>624</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>292</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>23920</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>277.25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>24889</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>155.25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>25958</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>107.5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1124.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1124.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="12">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,25 +37,16 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>سمن كريستال ابيض - 1.5 كجم</t>
-  </si>
-  <si>
-    <t>بيبسى كانز جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>كوكا كولا جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>فانتا برتقال جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>ماكسى كانز ليمون نعناع اورجينال - 300 مل</t>
-  </si>
-  <si>
-    <t>ماكسي بـرتقال - 2 لتر</t>
-  </si>
-  <si>
-    <t>بيبسي هضبه - 250 مل</t>
+    <t>بن عبد المعبود سادة فاتح - 50 جم</t>
+  </si>
+  <si>
+    <t>بن عبد المعبود محوج فاتح سوفت - 25 جم</t>
+  </si>
+  <si>
+    <t>بسكويت ماندولين بالشوكولاتة و الكراميل- 34 جم</t>
+  </si>
+  <si>
+    <t>بسكويت اوريو مغطى بالشوكلاتة 2 قطع - 31.3 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -416,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -444,121 +435,138 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>17</v>
+        <v>951</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>600</v>
+        <v>291</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>434</v>
+        <v>951</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>298.5</v>
+        <v>3492</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>615</v>
+        <v>6627</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>305.5</v>
+        <v>2167.5</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>624</v>
+        <v>6627</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>292</v>
+        <v>361.25</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23920</v>
+        <v>8677</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>277.25</v>
+        <v>1197</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24889</v>
+        <v>8677</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>155.25</v>
+        <v>99.75</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>25958</v>
+        <v>12058</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>107.5</v>
+        <v>100.75</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>12058</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1612</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1124.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1124.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,16 +37,31 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>بن عبد المعبود سادة فاتح - 50 جم</t>
-  </si>
-  <si>
-    <t>بن عبد المعبود محوج فاتح سوفت - 25 جم</t>
-  </si>
-  <si>
-    <t>بسكويت ماندولين بالشوكولاتة و الكراميل- 34 جم</t>
-  </si>
-  <si>
-    <t>بسكويت اوريو مغطى بالشوكلاتة 2 قطع - 31.3 جم</t>
+    <t>راني عصير خوخ حبيبات- 235 مل</t>
+  </si>
+  <si>
+    <t>راني عصير فراولة وموز حبيبات- 235 مل</t>
+  </si>
+  <si>
+    <t>بن عبد المعبود سادة فاتح سوفت - 50 جم</t>
+  </si>
+  <si>
+    <t>بيبسى - 1.47 لتر</t>
+  </si>
+  <si>
+    <t>راني عصير مشروب فراولة وموز - 235 مل</t>
+  </si>
+  <si>
+    <t>راني عصير مشروب  مانجو - 235 مل</t>
+  </si>
+  <si>
+    <t>بونكس اتوماتيك لافندر (كرتونة 3 كيس) - 4.5 كجم</t>
+  </si>
+  <si>
+    <t>ارز ثمرات عريض - 1 كجم</t>
+  </si>
+  <si>
+    <t>بونكس اوتوماتيك بلمسة الداوني - 9 كجم</t>
   </si>
   <si>
     <t>YES</t>
@@ -407,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -435,138 +450,172 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>951</v>
+        <v>202</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>291</v>
+        <v>395</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>951</v>
+        <v>332</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>3492</v>
+        <v>398</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>6627</v>
+        <v>6630</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>2167.5</v>
+        <v>290.25</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>6627</v>
+        <v>6630</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>361.25</v>
+        <v>3483</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>8677</v>
+        <v>8915</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>1197</v>
+        <v>185</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>8677</v>
+        <v>11290</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>99.75</v>
+        <v>321.75</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>12058</v>
+        <v>11304</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>100.75</v>
+        <v>318.25</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>12058</v>
+        <v>12048</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>1612</v>
+        <v>634.25</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>12930</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>278.25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22361</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>694</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1124.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1124.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="18">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,31 +37,34 @@
     <t>Tags</t>
   </si>
   <si>
+    <t>سفن اب ستار كانز - 320 مل</t>
+  </si>
+  <si>
+    <t>مرقة ماجى دجاج شريط - 8 جم</t>
+  </si>
+  <si>
     <t>راني عصير خوخ حبيبات- 235 مل</t>
   </si>
   <si>
-    <t>راني عصير فراولة وموز حبيبات- 235 مل</t>
-  </si>
-  <si>
-    <t>بن عبد المعبود سادة فاتح سوفت - 50 جم</t>
-  </si>
-  <si>
-    <t>بيبسى - 1.47 لتر</t>
-  </si>
-  <si>
-    <t>راني عصير مشروب فراولة وموز - 235 مل</t>
-  </si>
-  <si>
-    <t>راني عصير مشروب  مانجو - 235 مل</t>
-  </si>
-  <si>
-    <t>بونكس اتوماتيك لافندر (كرتونة 3 كيس) - 4.5 كجم</t>
-  </si>
-  <si>
-    <t>ارز ثمرات عريض - 1 كجم</t>
-  </si>
-  <si>
-    <t>بونكس اوتوماتيك بلمسة الداوني - 9 كجم</t>
+    <t>بيبسى كانز ستار - 320 مل</t>
+  </si>
+  <si>
+    <t>راني عصير مانجو حبيبات- 235 مل</t>
+  </si>
+  <si>
+    <t>سائل اطباق وفير بلس ليمون اصفر - 725 جم</t>
+  </si>
+  <si>
+    <t>سفن اب 1.47 لتر</t>
+  </si>
+  <si>
+    <t>شاى ليبتون اخضر - 25 فتلة</t>
+  </si>
+  <si>
+    <t>شاى ليبتون اخضر بالنعناع - 25 فتلة</t>
+  </si>
+  <si>
+    <t>حفاضات جود كير مقاس 5 - 58 حفاضة</t>
   </si>
   <si>
     <t>YES</t>
@@ -422,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -450,7 +453,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>202</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -459,66 +462,66 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>395</v>
+        <v>334</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>332</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>398</v>
+        <v>774</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>6630</v>
+        <v>161</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>290.25</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>6630</v>
+        <v>202</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>3483</v>
+        <v>402.5</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>8915</v>
+        <v>326</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -527,15 +530,15 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>185</v>
+        <v>330</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>11290</v>
+        <v>563</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -544,78 +547,146 @@
         <v>2</v>
       </c>
       <c r="D7">
-        <v>321.75</v>
+        <v>398.5</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>11304</v>
+        <v>8600</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>318.25</v>
+        <v>200</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>12048</v>
+        <v>8938</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>634.25</v>
+        <v>185</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>12930</v>
+        <v>9796</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>278.25</v>
+        <v>1548</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22361</v>
+        <v>9796</v>
       </c>
       <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>32.25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>9797</v>
+      </c>
+      <c r="B12" t="s">
         <v>15</v>
       </c>
-      <c r="C11">
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>30.5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>9797</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13">
         <v>1</v>
       </c>
-      <c r="D11">
-        <v>694</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="D13">
+        <v>1464</v>
+      </c>
+      <c r="E13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>9998</v>
+      </c>
+      <c r="B14" t="s">
         <v>16</v>
+      </c>
+      <c r="C14">
+        <v>29</v>
+      </c>
+      <c r="D14">
+        <v>741.75</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>9998</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15">
+        <v>80</v>
+      </c>
+      <c r="D15">
+        <v>247.25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1124.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1124.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,10 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>شويبس ليمون نعناع جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>كل يوم عصير جوافة  - 200 مل</t>
+    <t>شويبس ليمون نعناع  بلاستيك - 250 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -401,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -429,7 +426,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>5490</v>
+        <v>11683</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -438,27 +435,10 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>290</v>
+        <v>109.75</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>11835</v>
-      </c>
-      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>119</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1124.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1124.xlsx
@@ -37,7 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>شويبس ليمون نعناع  بلاستيك - 250 مل</t>
+    <t>مسحوق باهي يدوي لافندر  - 60 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -426,16 +426,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>11683</v>
+        <v>24567</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>109.75</v>
+        <v>88.75</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>

--- a/Pricing Logic/modules/uploads/module_4_1124.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1124.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="25">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,55 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>مسحوق باهي يدوي لافندر  - 60 جم</t>
+    <t>شويبس يوسفى جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>باندا مثلثات - 8 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مثلثات - 8 قطعه</t>
+  </si>
+  <si>
+    <t>ديرى مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>جبنة باندا رومى - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا رومى - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا بلس  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا  - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا بلس - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا 250 جرام</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا 125 جرام</t>
+  </si>
+  <si>
+    <t>عرض باندا ( 2علبة باندا250 جم + علبة فول باندا 400جم) - 900 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,19 +474,342 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24567</v>
+        <v>6931</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>285</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21704</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>88.75</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D3">
+        <v>693</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21704</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>19.25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21706</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>26.75</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21706</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>963</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21713</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>630</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21713</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>26.25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21752</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>474.25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21771</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>417.5</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21773</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>368.5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21774</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>474.25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21777</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>368.5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21778</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>474.25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21779</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>417.5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21781</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>283</v>
+      </c>
+      <c r="E16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>21783</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>356.5</v>
+      </c>
+      <c r="E17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>21789</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>310</v>
+      </c>
+      <c r="E18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>22125</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>474.25</v>
+      </c>
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>22126</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>368.5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>25775</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>280</v>
+      </c>
+      <c r="E21" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1124.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1124.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,55 +37,64 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>شويبس يوسفى جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>باندا مثلثات - 8 قطعه</t>
-  </si>
-  <si>
-    <t>باندا جورمية مثلثات - 8 قطعه</t>
-  </si>
-  <si>
-    <t>ديرى مثلثات - 16 قطعه</t>
-  </si>
-  <si>
-    <t>جبنة باندا رومى - 250 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا رومى - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا شيدر  - 125 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا شيدر - 250 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا بسطرمة  - 125 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا بسطرمة - 250 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا بسطرمة - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنة ديرى فيتا بلس  - 125 جم</t>
-  </si>
-  <si>
-    <t>جبنة ديرى فيتا  - 250 جم</t>
-  </si>
-  <si>
-    <t>جبنة ديرى فيتا بلس - 500 جم</t>
-  </si>
-  <si>
-    <t>جبنة باندا فيتا 250 جرام</t>
-  </si>
-  <si>
-    <t>جبنة باندا فيتا 125 جرام</t>
-  </si>
-  <si>
-    <t>عرض باندا ( 2علبة باندا250 جم + علبة فول باندا 400جم) - 900 جم</t>
+    <t>زيت كريستال الممتاز خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 900 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 6 زجاجة - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 4 زجاجة - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 6 زجاجة - 1.6 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 6 زجاجة - 1.6 لتر</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 900 مل</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة - 3.5 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس - 5 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1.8 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 2.4 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 6 زجاجة - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال الممتاز خليط - 2.5 لتر</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 550 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -474,24 +483,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>6931</v>
+        <v>448</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>285</v>
+        <v>625</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21704</v>
+        <v>823</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -500,316 +509,316 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>693</v>
+        <v>764.5</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21704</v>
+        <v>1490</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>19.25</v>
+        <v>604</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21706</v>
+        <v>1492</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>26.75</v>
+        <v>860</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21706</v>
+        <v>2878</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>963</v>
+        <v>388.25</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21713</v>
+        <v>2879</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>630</v>
+        <v>810</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21713</v>
+        <v>2916</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>26.25</v>
+        <v>955</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21752</v>
+        <v>2934</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>474.25</v>
+        <v>1066</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21771</v>
+        <v>2935</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>417.5</v>
+        <v>892.5</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21773</v>
+        <v>6496</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>368.5</v>
+        <v>758</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21774</v>
+        <v>6497</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>474.25</v>
+        <v>855</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21777</v>
+        <v>7520</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>368.5</v>
+        <v>1464.75</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21778</v>
+        <v>9070</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>474.25</v>
+        <v>895</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21779</v>
+        <v>9358</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>417.5</v>
+        <v>554</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21781</v>
+        <v>11402</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>283</v>
+        <v>704</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21783</v>
+        <v>11961</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>356.5</v>
+        <v>533.25</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21789</v>
+        <v>11965</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>310</v>
+        <v>705.25</v>
       </c>
       <c r="E18" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22125</v>
+        <v>12923</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>474.25</v>
+        <v>855</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22126</v>
+        <v>12924</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>368.5</v>
+        <v>600</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>25775</v>
+        <v>12925</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>280</v>
+        <v>490</v>
       </c>
       <c r="E21" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1124.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1124.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,64 +37,19 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>زيت كريستال الممتاز خليط - 700 مل</t>
-  </si>
-  <si>
     <t>زيت حبوبة خليط - 900 مل</t>
   </si>
   <si>
-    <t>زيت حبوبة خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 6 زجاجة - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة 4 زجاجة - 2.2 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة 6 زجاجة - 1.6 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 6 زجاجة - 1.6 لتر</t>
-  </si>
-  <si>
-    <t>سندة زيت خليط - 900 مل</t>
-  </si>
-  <si>
-    <t>سندة زيت خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة - 3.5 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس - 5 لتر</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 1.8 لتر</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 2.4 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 6 زجاجة - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال الممتاز خليط - 2.5 لتر</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 550 مل</t>
+    <t>دومتي جبنة فيتا بلس - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة اسطنبولي بلس - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس بسطرمة - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس لايت - 500 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -455,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -483,7 +438,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>448</v>
+        <v>823</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -492,333 +447,78 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>625</v>
+        <v>777</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>823</v>
+        <v>19981</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>764.5</v>
+        <v>460</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>1490</v>
+        <v>19985</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>604</v>
+        <v>460</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>1492</v>
+        <v>19989</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>860</v>
+        <v>460</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>2878</v>
+        <v>19997</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>388.25</v>
+        <v>460</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>2879</v>
-      </c>
-      <c r="B7" t="s">
         <v>12</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>810</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>2916</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>955</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>2934</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1066</v>
-      </c>
-      <c r="E9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>2935</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>892.5</v>
-      </c>
-      <c r="E10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>6496</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>758</v>
-      </c>
-      <c r="E11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>6497</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>855</v>
-      </c>
-      <c r="E12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>7520</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>1464.75</v>
-      </c>
-      <c r="E13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>9070</v>
-      </c>
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>895</v>
-      </c>
-      <c r="E14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>9358</v>
-      </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>554</v>
-      </c>
-      <c r="E15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>11402</v>
-      </c>
-      <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>704</v>
-      </c>
-      <c r="E16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>11961</v>
-      </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>533.25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>11965</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>705.25</v>
-      </c>
-      <c r="E18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>12923</v>
-      </c>
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>855</v>
-      </c>
-      <c r="E19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>12924</v>
-      </c>
-      <c r="B20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>600</v>
-      </c>
-      <c r="E20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>12925</v>
-      </c>
-      <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>490</v>
-      </c>
-      <c r="E21" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_1124.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_1124.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,19 +37,37 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>زيت حبوبة خليط - 900 مل</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس - 500 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة اسطنبولي بلس - 500 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس بسطرمة - 500 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس لايت - 500 جم</t>
+    <t>صابون كامى اناقة -- 110 جم</t>
+  </si>
+  <si>
+    <t>صابون كامى حيوية - 110 جم</t>
+  </si>
+  <si>
+    <t>صابون كامى كلاسيك -- 110 جم</t>
+  </si>
+  <si>
+    <t>صابون كامى رومانسية - 110 جم</t>
+  </si>
+  <si>
+    <t>لوكس صابون حلم السعادة  - 115 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس بشرة مثالية - 115 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس بشرة نضرة - 115 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس سحر الاوركيد - 115 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس بشرة نضرة - 165 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس سحر الاوركيد - 165 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس بشرة مثالية - 165 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -410,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -438,87 +456,376 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>823</v>
+        <v>8283</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>777</v>
+        <v>60.5</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19981</v>
+        <v>8283</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>460</v>
+        <v>726</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19985</v>
+        <v>8284</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4">
-        <v>460</v>
+        <v>60.5</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19989</v>
+        <v>8284</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>460</v>
+        <v>726</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19997</v>
+        <v>8285</v>
       </c>
       <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>60.5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>8285</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>726</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>8286</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>60.5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>8286</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>726</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>9065</v>
+      </c>
+      <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>460</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>94.25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>9065</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>754</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>11687</v>
+      </c>
+      <c r="B12" t="s">
         <v>12</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>94.25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>11687</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>754</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>11689</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>94.25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>11689</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>754</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>11690</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>94.25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>11690</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>754</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>11885</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>152.5</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>11885</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1220</v>
+      </c>
+      <c r="E19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>11886</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>152.5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>11886</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1220</v>
+      </c>
+      <c r="E21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>11887</v>
+      </c>
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>152.5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>11887</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1220</v>
+      </c>
+      <c r="E23" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
